--- a/output/pdf_financials_xlsx/BES.xlsx
+++ b/output/pdf_financials_xlsx/BES.xlsx
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.005973</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00173</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001318</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -882,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.012724</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.021535</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000691</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00099</v>
       </c>
     </row>
     <row r="13">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.17025</v>
+        <v>-0.176223</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.172136</v>
+        <v>-0.173866</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.134185</v>
+        <v>-0.135503</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.325745</v>
@@ -1574,16 +1574,16 @@
         <v>-0.734477</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.769193</v>
+        <v>-2.781917</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.907333</v>
+        <v>-2.928868</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.647902</v>
+        <v>-2.648593</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.605692</v>
+        <v>-1.606682</v>
       </c>
     </row>
     <row r="28">
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.17025</v>
+        <v>-0.176223</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.172136</v>
+        <v>-0.173866</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.134185</v>
+        <v>-0.135503</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.325745</v>
@@ -1654,16 +1654,16 @@
         <v>-0.734477</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.769193</v>
+        <v>-2.781917</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.907333</v>
+        <v>-2.928868</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.647902</v>
+        <v>-2.648593</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.605692</v>
+        <v>-1.606682</v>
       </c>
     </row>
     <row r="30">
@@ -1702,16 +1702,16 @@
         <v>-21.18723787364049</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-67.54368142287959</v>
+        <v>-67.85403386217318</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-77.32881489011629</v>
+        <v>-77.90159964805721</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-78.54453488672172</v>
+        <v>-78.56503197219041</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-51.08262816134391</v>
+        <v>-51.11412349287681</v>
       </c>
     </row>
     <row r="31">
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.411106</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.212783</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.107245</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002457</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.621845</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -1836,19 +1836,19 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>4.207099</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.475869</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.140278</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.104347</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.108674</v>
       </c>
     </row>
     <row r="35">
@@ -1900,19 +1900,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.411106</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.212783</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.107245</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002457</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.621845</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
@@ -1920,19 +1920,19 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>4.207099</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.16125</v>
+        <v>2.637119</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.10925</v>
+        <v>0.249528</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.0372</v>
+        <v>0.141547</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.108674</v>
       </c>
     </row>
     <row r="37">
@@ -2404,19 +2404,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.529702</v>
+        <v>0.118596</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.332856</v>
+        <v>0.120073</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.145907</v>
+        <v>0.038662</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.211265</v>
+        <v>0.208808</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.785502</v>
+        <v>0.163657</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
@@ -2424,19 +2424,19 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.502228</v>
+        <v>0.295129</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.826576</v>
+        <v>0.350707</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.47416</v>
+        <v>0.333882</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.348016</v>
+        <v>0.243669</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.627062</v>
+        <v>0.518388</v>
       </c>
     </row>
     <row r="49">
@@ -5613,19 +5613,19 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.116928</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.159369</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.167748</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-0.044291</v>
+        <v>-0.215048</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-0.007564</v>
+        <v>-0.183644</v>
       </c>
     </row>
     <row r="125">
@@ -5653,19 +5653,19 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.116928</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.159369</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.167748</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-0.044291</v>
+        <v>-0.215048</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-0.007564</v>
+        <v>-0.183644</v>
       </c>
     </row>
     <row r="126">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -14025,7 +14025,11 @@
           <t>Lease payments (Note 20)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -15450,7 +15454,11 @@
           <t>Lease payments (Note 21)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -21424,7 +21432,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -22480,7 +22488,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E239" s="5" t="n">

--- a/output/pdf_financials_xlsx/BES.xlsx
+++ b/output/pdf_financials_xlsx/BES.xlsx
@@ -1605,25 +1605,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.037778</v>
+        <v>0.006561</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.153212</v>
+        <v>0.031563</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.09804300000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.09855700000000001</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.128112</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.130659</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.130731</v>
       </c>
     </row>
     <row r="29">
@@ -1645,25 +1645,25 @@
         <v>-0.325745</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.491126</v>
+        <v>-2.522343</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.759994</v>
+        <v>-2.881643</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.734477</v>
+        <v>-0.6364340000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.781917</v>
+        <v>-2.68336</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.928868</v>
+        <v>-2.800756</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.648593</v>
+        <v>-2.517934</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.606682</v>
+        <v>-1.475951</v>
       </c>
     </row>
     <row r="30">
@@ -1693,25 +1693,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-360.4054392282418</v>
+        <v>-364.9217810738121</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-110.3685036397692</v>
+        <v>-115.2330859900476</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-21.18723787364049</v>
+        <v>-18.35902083914474</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-67.85403386217318</v>
+        <v>-65.45011957739969</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-77.90159964805721</v>
+        <v>-74.49409554267865</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-78.56503197219041</v>
+        <v>-74.68930304273449</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-51.11412349287681</v>
+        <v>-46.95511724375764</v>
       </c>
     </row>
     <row r="31">
@@ -4647,25 +4647,25 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.037778</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.153212</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.115706</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.144648</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.168909</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.171658</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.171731</v>
       </c>
     </row>
     <row r="101">
@@ -13073,7 +13073,11 @@
           <t>Depreciation of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -13136,7 +13140,11 @@
           <t>Depreciation of right of use assets (Note 8)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -15957,7 +15965,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -21168,7 +21176,11 @@
           <t>Depreciation of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -21231,7 +21243,11 @@
           <t>Depreciation of right of use assets (Note 8)</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -24718,7 +24734,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
